--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486297_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486297_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.0022</v>
+        <v>5.9773</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0081</v>
+        <v>5.9216</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0059</v>
+        <v>0.0557</v>
       </c>
       <c r="G2" t="n">
         <v>3.1704</v>
@@ -610,13 +610,13 @@
         <v>0.6525</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6371</v>
+        <v>0.6123</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7607</v>
+        <v>0.6742</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1235</v>
+        <v>-0.0619</v>
       </c>
       <c r="V2" t="n">
         <v>2.6297</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0648</v>
+        <v>3.1525</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9666</v>
+        <v>3.1468</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0982</v>
+        <v>0.0057</v>
       </c>
       <c r="G3" t="n">
         <v>1.7889</v>
@@ -688,13 +688,13 @@
         <v>1.5225</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2467</v>
+        <v>-0.1589</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0649</v>
+        <v>0.1154</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1818</v>
+        <v>-0.2743</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6193</v>
+        <v>0.7927</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0674</v>
+        <v>1.1792</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4481</v>
+        <v>-0.3865</v>
       </c>
       <c r="G4" t="n">
         <v>0.8077</v>
@@ -766,13 +766,13 @@
         <v>1.5225</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6234</v>
+        <v>-0.45</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6044</v>
+        <v>-0.4927</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.019</v>
+        <v>0.0427</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2681</v>
+        <v>-0.3156</v>
       </c>
       <c r="E5" t="n">
-        <v>4.1107</v>
+        <v>3.4654</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.8427</v>
+        <v>-3.781</v>
       </c>
       <c r="G5" t="n">
         <v>1.2981</v>
@@ -844,13 +844,13 @@
         <v>0.6525</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9472</v>
+        <v>0.3635</v>
       </c>
       <c r="T5" t="n">
-        <v>1.7112</v>
+        <v>1.0659</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.764</v>
+        <v>-0.7024</v>
       </c>
       <c r="V5" t="n">
         <v>-2.6297</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. SEOANE RODICIO</t>
+          <t>A. PARRADO CALABRIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.3104</v>
+        <v>-2.1562</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2702</v>
+        <v>-1.6466</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.5806</v>
+        <v>-0.5096000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>0.08840000000000001</v>
+        <v>-2.1941</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4167</v>
+        <v>-0.0697</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3283</v>
+        <v>-2.1244</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6281</v>
+        <v>-0.8743</v>
       </c>
       <c r="K6" t="n">
-        <v>0.703</v>
+        <v>0.2317</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.07489999999999999</v>
+        <v>-1.106</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5397</v>
+        <v>-1.3197</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2863</v>
+        <v>-0.3013</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2534</v>
+        <v>-1.0184</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.2175</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R6" t="n">
-        <v>1.0875</v>
+        <v>1.305</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3134</v>
+        <v>-0.0051</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5997</v>
+        <v>-0.2704</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.9131</v>
+        <v>0.2653</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.0854</v>
+        <v>-0.1745</v>
       </c>
       <c r="W6" t="n">
-        <v>1.13</v>
+        <v>0.5857</v>
       </c>
       <c r="X6" t="n">
-        <v>-3.2154</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. PARRADO CALABRIA</t>
+          <t>J. ZIDEK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.456</v>
+        <v>-2.4582</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.1621</v>
+        <v>-0.901</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2939</v>
+        <v>-1.5572</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.1941</v>
+        <v>-1.8832</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0697</v>
+        <v>-0.9429</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.1244</v>
+        <v>-0.9403</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.8743</v>
+        <v>-0.6703</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2317</v>
+        <v>0.0365</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.106</v>
+        <v>-0.7068</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.3197</v>
+        <v>-1.2129</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3013</v>
+        <v>-0.9794</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.0184</v>
+        <v>-0.2335</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2175</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.305</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3049</v>
+        <v>-0.575</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7859</v>
+        <v>-0.2307</v>
       </c>
       <c r="U7" t="n">
-        <v>0.481</v>
+        <v>-0.3443</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1745</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5857</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.7602</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. ZIDEK</t>
+          <t>R. SEOANE RODICIO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.6316</v>
+        <v>-2.6705</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0128</v>
+        <v>0.8484</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.6188</v>
+        <v>-3.5189</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.8832</v>
+        <v>0.08840000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.9429</v>
+        <v>0.4167</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9403</v>
+        <v>-0.3283</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6703</v>
+        <v>0.6281</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0365</v>
+        <v>0.703</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7068</v>
+        <v>-0.07489999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.2129</v>
+        <v>-0.5397</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9794</v>
+        <v>-0.2863</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2335</v>
+        <v>-0.2534</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.0875</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7484</v>
+        <v>-0.6736</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3425</v>
+        <v>0.1779</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4059</v>
+        <v>-0.8514</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-2.0854</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-3.2154</v>
       </c>
     </row>
     <row r="9">
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.9866</v>
+        <v>-2.7631</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9658</v>
+        <v>-1.7423</v>
       </c>
       <c r="F9" t="n">
         <v>-1.0207</v>
@@ -1156,10 +1156,10 @@
         <v>1.5225</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0311</v>
+        <v>-0.8075</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.4494</v>
       </c>
       <c r="U9" t="n">
         <v>-0.3581</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.857</v>
+        <v>-3.7739</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.1376</v>
+        <v>-3.7771</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2806</v>
+        <v>0.0032</v>
       </c>
       <c r="G10" t="n">
         <v>-2.184</v>
@@ -1234,13 +1234,13 @@
         <v>1.0875</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5445</v>
+        <v>0.6276</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1646</v>
+        <v>0.5252</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3798</v>
+        <v>0.1024</v>
       </c>
       <c r="V10" t="n">
         <v>-1.13</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.5334</v>
+        <v>-7.9208</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.6612</v>
+        <v>-5.3259</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.8722</v>
+        <v>-2.5948</v>
       </c>
       <c r="G11" t="n">
         <v>-6.797</v>
@@ -1312,13 +1312,13 @@
         <v>1.5225</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.781</v>
+        <v>-1.1683</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0719</v>
+        <v>-0.7366</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7091</v>
+        <v>-0.4317</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3904</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-12.8206</v>
+        <v>-12.1358</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4834999999999994</v>
+        <v>1.168500000000002</v>
       </c>
       <c r="F12" t="n">
         <v>-13.3041</v>
@@ -1372,10 +1372,10 @@
         <v>-2.5817</v>
       </c>
       <c r="M12" t="n">
-        <v>-9.464499999999999</v>
+        <v>-9.464500000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>-4.595400000000001</v>
+        <v>-4.5954</v>
       </c>
       <c r="O12" t="n">
         <v>-4.869</v>
@@ -1390,10 +1390,10 @@
         <v>10.875</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.9201</v>
+        <v>-2.235</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3063000000000001</v>
+        <v>0.3788000000000001</v>
       </c>
       <c r="U12" t="n">
         <v>-2.6137</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.8248</v>
+        <v>4.2345</v>
       </c>
       <c r="E13" t="n">
-        <v>6.2162</v>
+        <v>6.328</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.3914</v>
+        <v>-2.0934</v>
       </c>
       <c r="G13" t="n">
         <v>4.4904</v>
@@ -1468,13 +1468,13 @@
         <v>0.435</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7895</v>
+        <v>1.1993</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6682</v>
+        <v>0.7799</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1214</v>
+        <v>0.4194</v>
       </c>
       <c r="V13" t="n">
         <v>-1.8902</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. THIAM</t>
+          <t>I. DIOP GAYE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.0824</v>
+        <v>3.4498</v>
       </c>
       <c r="E14" t="n">
-        <v>3.0488</v>
+        <v>0.8815</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0336</v>
+        <v>2.5683</v>
       </c>
       <c r="G14" t="n">
-        <v>0.49</v>
+        <v>2.5731</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0063</v>
+        <v>2.7038</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4837</v>
+        <v>-0.1307</v>
       </c>
       <c r="J14" t="n">
-        <v>1.3452</v>
+        <v>2.2513</v>
       </c>
       <c r="K14" t="n">
-        <v>1.2687</v>
+        <v>2.1931</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0765</v>
+        <v>0.0582</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.8552</v>
+        <v>0.3218</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.2624</v>
+        <v>0.5107</v>
       </c>
       <c r="O14" t="n">
-        <v>0.4072</v>
+        <v>-0.1889</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>-1.305</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R14" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8974</v>
+        <v>1.0725</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5312</v>
+        <v>0.2403</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3663</v>
+        <v>0.8322000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>1.695</v>
+        <v>1.1093</v>
       </c>
       <c r="W14" t="n">
-        <v>2.2599</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0.5443</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I. DIOP GAYE</t>
+          <t>A. THIAM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.9784</v>
+        <v>2.7498</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7698</v>
+        <v>2.937</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2086</v>
+        <v>-0.1873</v>
       </c>
       <c r="G15" t="n">
-        <v>2.5731</v>
+        <v>0.49</v>
       </c>
       <c r="H15" t="n">
-        <v>2.7038</v>
+        <v>0.0063</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1307</v>
+        <v>0.4837</v>
       </c>
       <c r="J15" t="n">
-        <v>2.2513</v>
+        <v>1.3452</v>
       </c>
       <c r="K15" t="n">
-        <v>2.1931</v>
+        <v>1.2687</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0582</v>
+        <v>0.0765</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3218</v>
+        <v>-0.8552</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5107</v>
+        <v>-1.2624</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1889</v>
+        <v>0.4072</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.305</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R15" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6011</v>
+        <v>0.5648</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1286</v>
+        <v>0.4194</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4725</v>
+        <v>0.1454</v>
       </c>
       <c r="V15" t="n">
-        <v>1.1093</v>
+        <v>1.695</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5649999999999999</v>
+        <v>2.2599</v>
       </c>
       <c r="X15" t="n">
-        <v>0.5443</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.508</v>
+        <v>2.2665</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9272</v>
+        <v>1.4802</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5808</v>
+        <v>0.7864</v>
       </c>
       <c r="G16" t="n">
         <v>1.8062</v>
@@ -1702,13 +1702,13 @@
         <v>0.435</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2244</v>
+        <v>-0.0171</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8051</v>
+        <v>0.3581</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5808</v>
+        <v>-0.3752</v>
       </c>
       <c r="V16" t="n">
         <v>1.13</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.3962</v>
+        <v>1.3236</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0389</v>
+        <v>1.033</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3573</v>
+        <v>0.2906</v>
       </c>
       <c r="G17" t="n">
         <v>-1.8886</v>
@@ -1780,13 +1780,13 @@
         <v>1.305</v>
       </c>
       <c r="S17" t="n">
-        <v>1.8498</v>
+        <v>0.7772</v>
       </c>
       <c r="T17" t="n">
-        <v>1.4132</v>
+        <v>0.4074</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4366</v>
+        <v>0.3698</v>
       </c>
       <c r="V17" t="n">
         <v>1.13</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. JOU COLL</t>
+          <t>J. CREMO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.8094</v>
+        <v>1.1367</v>
       </c>
       <c r="E18" t="n">
-        <v>2.2254</v>
+        <v>-0.7184</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.416</v>
+        <v>1.8551</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2564</v>
+        <v>-1.1323</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.9671999999999999</v>
+        <v>-0.7538</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7108</v>
+        <v>-0.3785</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1001</v>
+        <v>-1.3537</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6173</v>
+        <v>-0.419</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5172</v>
+        <v>-0.9347</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1563</v>
+        <v>0.2214</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3499</v>
+        <v>-0.3348</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1936</v>
+        <v>0.5562</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5225</v>
+        <v>0.435</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R18" t="n">
         <v>1.5225</v>
       </c>
       <c r="S18" t="n">
-        <v>1.2828</v>
+        <v>-0.426</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8051</v>
+        <v>-0.5371</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4777</v>
+        <v>0.1111</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.7395</v>
+        <v>2.2599</v>
       </c>
       <c r="W18" t="n">
-        <v>1.5204</v>
+        <v>2.2599</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.2599</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. CREMO</t>
+          <t>G. JOU COLL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2182</v>
+        <v>1.1338</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2772</v>
+        <v>1.5549</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4954</v>
+        <v>-0.4211</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.1323</v>
+        <v>-0.2564</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.7538</v>
+        <v>-0.9671999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3785</v>
+        <v>0.7108</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.3537</v>
+        <v>-0.1001</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.419</v>
+        <v>-0.6173</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.9347</v>
+        <v>0.5172</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2214</v>
+        <v>-0.1563</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3348</v>
+        <v>-0.3499</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5562</v>
+        <v>0.1936</v>
       </c>
       <c r="P19" t="n">
-        <v>0.435</v>
+        <v>1.5225</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>1.5225</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.3445</v>
+        <v>0.6072</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0959</v>
+        <v>0.1346</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2485</v>
+        <v>0.4726</v>
       </c>
       <c r="V19" t="n">
-        <v>2.2599</v>
+        <v>-0.7395</v>
       </c>
       <c r="W19" t="n">
-        <v>2.2599</v>
+        <v>1.5204</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. VARELA ROMERO</t>
+          <t>P. JORGENSEN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0633</v>
+        <v>0.8848</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0365</v>
+        <v>0.5329</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0268</v>
+        <v>0.3519</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.197</v>
+        <v>-1.5198</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0365</v>
+        <v>-0.7389</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2335</v>
+        <v>-0.7809</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0365</v>
+        <v>-1.3427</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0365</v>
+        <v>-0.0056</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-1.3371</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2335</v>
+        <v>-0.1771</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>-0.7333</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2335</v>
+        <v>0.5562</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.435</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>0.435</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2603</v>
+        <v>0.6444</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>0.5504</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2603</v>
+        <v>0.094</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.3252</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.3252</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. JORGENSEN</t>
+          <t>C. VARELA ROMERO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4343</v>
+        <v>0.0518</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0259</v>
+        <v>0.1483</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4084</v>
+        <v>-0.0965</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.5198</v>
+        <v>-0.197</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.7389</v>
+        <v>0.0365</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7809</v>
+        <v>-0.2335</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.3427</v>
+        <v>0.0365</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.0056</v>
+        <v>0.0365</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.3371</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1771</v>
+        <v>-0.2335</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7333</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5562</v>
+        <v>-0.2335</v>
       </c>
       <c r="P21" t="n">
-        <v>0.435</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.435</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6748</v>
+        <v>0.2488</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.1118</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6663</v>
+        <v>0.137</v>
       </c>
       <c r="V21" t="n">
-        <v>1.3252</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.3252</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.6387</v>
+        <v>-0.2366</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8041</v>
+        <v>-0.9159</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1655</v>
+        <v>0.6792</v>
       </c>
       <c r="G22" t="n">
         <v>1.562</v>
@@ -2170,13 +2170,13 @@
         <v>1.5225</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4606</v>
+        <v>-0.0586</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2572</v>
+        <v>0.1454</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7178</v>
+        <v>-0.204</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,10 +2203,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.9881</v>
+        <v>-0.6528</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5742</v>
+        <v>0.9095</v>
       </c>
       <c r="F23" t="n">
         <v>-1.5623</v>
@@ -2248,10 +2248,10 @@
         <v>0.2175</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.173</v>
+        <v>0.1622</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.411</v>
+        <v>-0.0757</v>
       </c>
       <c r="U23" t="n">
         <v>0.2379</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.9989</v>
+        <v>-1.286</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.2303</v>
+        <v>-0.6715</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.7685999999999999</v>
+        <v>-0.6145</v>
       </c>
       <c r="G24" t="n">
         <v>0.248</v>
@@ -2326,13 +2326,13 @@
         <v>0.435</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3323</v>
+        <v>0.3806</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4795</v>
+        <v>0.0793</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1472</v>
+        <v>0.3013</v>
       </c>
       <c r="V24" t="n">
         <v>-0.1745</v>
@@ -2359,22 +2359,22 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>12.8207</v>
+        <v>15.0559</v>
       </c>
       <c r="E25" t="n">
         <v>13.4995</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.6787000000000001</v>
+        <v>1.5564</v>
       </c>
       <c r="G25" t="n">
         <v>7.2078</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.2428999999999998</v>
+        <v>-0.2428999999999996</v>
       </c>
       <c r="I25" t="n">
-        <v>7.450599999999999</v>
+        <v>7.450600000000001</v>
       </c>
       <c r="J25" t="n">
         <v>9.464600000000001</v>
@@ -2401,19 +2401,19 @@
         <v>-10.8753</v>
       </c>
       <c r="R25" t="n">
-        <v>9.787499999999998</v>
+        <v>9.7875</v>
       </c>
       <c r="S25" t="n">
-        <v>2.920100000000001</v>
+        <v>5.1553</v>
       </c>
       <c r="T25" t="n">
         <v>2.6138</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3064999999999999</v>
+        <v>2.5415</v>
       </c>
       <c r="V25" t="n">
-        <v>3.780499999999999</v>
+        <v>3.7805</v>
       </c>
       <c r="W25" t="n">
         <v>12.2965</v>
